--- a/artfynd/A 58348-2025 artfynd.xlsx
+++ b/artfynd/A 58348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130119246</v>
       </c>
       <c r="B2" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130106544</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58348-2025 artfynd.xlsx
+++ b/artfynd/A 58348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130119246</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130106544</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>92146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58348-2025 artfynd.xlsx
+++ b/artfynd/A 58348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130119246</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130106544</v>
       </c>
       <c r="B3" t="n">
-        <v>92146</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58348-2025 artfynd.xlsx
+++ b/artfynd/A 58348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130119246</v>
       </c>
       <c r="B2" t="n">
-        <v>92163</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130106544</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>92175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58348-2025 artfynd.xlsx
+++ b/artfynd/A 58348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130119246</v>
       </c>
       <c r="B2" t="n">
-        <v>92189</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130106544</v>
       </c>
       <c r="B3" t="n">
-        <v>92175</v>
+        <v>92328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
